--- a/Plan/Table/LiveData/03.RelicData.xlsx
+++ b/Plan/Table/LiveData/03.RelicData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDAB4FD4-282F-4C44-A1F8-FAB7B8A8687A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66DDD4AC-077C-4B65-BC9E-4084B33558DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{614179A6-8783-4F7F-B09D-80AD4CD3E845}"/>
+    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{899E5EC9-8592-4929-9544-8D278BD3314F}"/>
   </bookViews>
   <sheets>
     <sheet name="03.RelicData" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -1411,7 +1414,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2B47B1B-ECBD-4B70-8E65-11C010907A8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4617F4B1-6B11-48E7-A56E-1668B79DFAF6}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:O80"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Plan/Table/LiveData/03.RelicData.xlsx
+++ b/Plan/Table/LiveData/03.RelicData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66DDD4AC-077C-4B65-BC9E-4084B33558DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6B00F57-774F-4852-B30C-B6F0109BD730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{899E5EC9-8592-4929-9544-8D278BD3314F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AE4B9E2C-D86D-4DC5-BEBC-398BB4DCDB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="03.RelicData" sheetId="1" r:id="rId1"/>
@@ -1414,8 +1414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4617F4B1-6B11-48E7-A56E-1668B79DFAF6}">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCEDD43F-A03B-409A-9F41-BACD713C8554}">
   <dimension ref="A1:O80"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1483,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="G2">
         <v>0</v>
